--- a/yearly.xlsx
+++ b/yearly.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,40 +476,48 @@
           <t>Tencent</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SP500</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="B2" t="n">
-        <v>19.00607109069824</v>
+        <v>16.05835914611816</v>
       </c>
       <c r="C2" t="n">
-        <v>26.70999908447266</v>
+        <v>21.37443923950195</v>
       </c>
       <c r="D2" t="n">
-        <v>17.70220184326172</v>
+        <v>17.53533935546875</v>
       </c>
       <c r="E2" t="n">
         <v>12.54349994659424</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3064999878406525</v>
+        <v>0.2821623682975769</v>
       </c>
       <c r="G2" t="n">
-        <v>26.6200008392334</v>
+        <v>26.36746025085449</v>
       </c>
       <c r="H2" t="n">
-        <v>30440</v>
+        <v>22761.587890625</v>
       </c>
       <c r="I2" t="n">
         <v>2.257999897003174</v>
       </c>
       <c r="J2" t="n">
-        <v>20.6200008392334</v>
+        <v>14.74580478668213</v>
       </c>
       <c r="K2" t="n">
-        <v>45.90845108032227</v>
+        <v>42.95567321777344</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1426.18994140625</v>
       </c>
     </row>
     <row r="3">
@@ -517,34 +525,37 @@
         <v>41639</v>
       </c>
       <c r="B3" t="n">
-        <v>20.03642845153809</v>
+        <v>17.35419082641602</v>
       </c>
       <c r="C3" t="n">
-        <v>37.40999984741211</v>
+        <v>30.8428897857666</v>
       </c>
       <c r="D3" t="n">
-        <v>28.04579544067383</v>
+        <v>27.78143692016602</v>
       </c>
       <c r="E3" t="n">
         <v>19.93950080871582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4004999995231628</v>
+        <v>0.3767540752887726</v>
       </c>
       <c r="G3" t="n">
-        <v>54.65000152587891</v>
+        <v>54.13154602050781</v>
       </c>
       <c r="H3" t="n">
-        <v>27440</v>
+        <v>20729.638671875</v>
       </c>
       <c r="I3" t="n">
         <v>10.02866744995117</v>
       </c>
       <c r="J3" t="n">
-        <v>25.95999908447266</v>
+        <v>19.30521774291992</v>
       </c>
       <c r="K3" t="n">
-        <v>91.19004058837891</v>
+        <v>85.64275360107422</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1848.359985351562</v>
       </c>
     </row>
     <row r="4">
@@ -552,34 +563,37 @@
         <v>42004</v>
       </c>
       <c r="B4" t="n">
-        <v>27.59499931335449</v>
+        <v>24.40390014648438</v>
       </c>
       <c r="C4" t="n">
-        <v>46.45000076293945</v>
+        <v>39.3446044921875</v>
       </c>
       <c r="D4" t="n">
-        <v>26.53300094604492</v>
+        <v>26.28290367126465</v>
       </c>
       <c r="E4" t="n">
         <v>15.51749992370605</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5012500286102295</v>
+        <v>0.4799688160419464</v>
       </c>
       <c r="G4" t="n">
-        <v>78.01999664306641</v>
+        <v>77.27983093261719</v>
       </c>
       <c r="H4" t="n">
-        <v>26540</v>
+        <v>20350.8203125</v>
       </c>
       <c r="I4" t="n">
         <v>14.82733345031738</v>
       </c>
       <c r="J4" t="n">
-        <v>36.29000091552734</v>
+        <v>27.84274673461914</v>
       </c>
       <c r="K4" t="n">
-        <v>103.7088470458984</v>
+        <v>97.63364410400391</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2058.89990234375</v>
       </c>
     </row>
     <row r="5">
@@ -587,34 +601,37 @@
         <v>42369</v>
       </c>
       <c r="B5" t="n">
-        <v>26.31500053405762</v>
+        <v>23.66843414306641</v>
       </c>
       <c r="C5" t="n">
-        <v>55.47999954223633</v>
+        <v>48.27262496948242</v>
       </c>
       <c r="D5" t="n">
-        <v>38.9005012512207</v>
+        <v>38.5338249206543</v>
       </c>
       <c r="E5" t="n">
         <v>33.79449844360352</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8240000009536743</v>
+        <v>0.8021025061607361</v>
       </c>
       <c r="G5" t="n">
-        <v>104.6600036621094</v>
+        <v>103.6671142578125</v>
       </c>
       <c r="H5" t="n">
-        <v>25200</v>
+        <v>19648.85546875</v>
       </c>
       <c r="I5" t="n">
         <v>16.00066757202148</v>
       </c>
       <c r="J5" t="n">
-        <v>34.45000076293945</v>
+        <v>27.2263240814209</v>
       </c>
       <c r="K5" t="n">
-        <v>140.5831146240234</v>
+        <v>132.6690673828125</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2043.93994140625</v>
       </c>
     </row>
     <row r="6">
@@ -622,34 +639,37 @@
         <v>42735</v>
       </c>
       <c r="B6" t="n">
-        <v>28.95499992370605</v>
+        <v>26.62235450744629</v>
       </c>
       <c r="C6" t="n">
-        <v>62.13999938964844</v>
+        <v>55.55104064941406</v>
       </c>
       <c r="D6" t="n">
-        <v>39.62250137329102</v>
+        <v>39.24901580810547</v>
       </c>
       <c r="E6" t="n">
         <v>37.49349975585938</v>
       </c>
       <c r="F6" t="n">
-        <v>2.668499946594238</v>
+        <v>2.622555732727051</v>
       </c>
       <c r="G6" t="n">
-        <v>115.0500030517578</v>
+        <v>113.9585342407227</v>
       </c>
       <c r="H6" t="n">
-        <v>36040</v>
+        <v>28557.615234375</v>
       </c>
       <c r="I6" t="n">
         <v>14.24600028991699</v>
       </c>
       <c r="J6" t="n">
-        <v>36.27000045776367</v>
+        <v>29.61037063598633</v>
       </c>
       <c r="K6" t="n">
-        <v>174.8761749267578</v>
+        <v>165.5685729980469</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2238.830078125</v>
       </c>
     </row>
     <row r="7">
@@ -657,34 +677,37 @@
         <v>43100</v>
       </c>
       <c r="B7" t="n">
-        <v>42.30749893188477</v>
+        <v>39.52470016479492</v>
       </c>
       <c r="C7" t="n">
-        <v>85.54000091552734</v>
+        <v>78.17729949951172</v>
       </c>
       <c r="D7" t="n">
-        <v>52.66999816894531</v>
+        <v>52.17353439331055</v>
       </c>
       <c r="E7" t="n">
         <v>58.4734992980957</v>
       </c>
       <c r="F7" t="n">
-        <v>4.837500095367432</v>
+        <v>4.772734642028809</v>
       </c>
       <c r="G7" t="n">
-        <v>176.4600067138672</v>
+        <v>174.7859497070312</v>
       </c>
       <c r="H7" t="n">
-        <v>50960</v>
+        <v>41112.21484375</v>
       </c>
       <c r="I7" t="n">
         <v>20.75666618347168</v>
       </c>
       <c r="J7" t="n">
-        <v>46.15999984741211</v>
+        <v>38.75113296508789</v>
       </c>
       <c r="K7" t="n">
-        <v>374.2737121582031</v>
+        <v>355.2437438964844</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2673.610107421875</v>
       </c>
     </row>
     <row r="8">
@@ -692,34 +715,37 @@
         <v>43465</v>
       </c>
       <c r="B8" t="n">
-        <v>39.43500137329102</v>
+        <v>37.39425277709961</v>
       </c>
       <c r="C8" t="n">
-        <v>101.5699996948242</v>
+        <v>94.43453979492188</v>
       </c>
       <c r="D8" t="n">
-        <v>52.24800109863281</v>
+        <v>51.75551223754883</v>
       </c>
       <c r="E8" t="n">
         <v>75.09850311279297</v>
       </c>
       <c r="F8" t="n">
-        <v>3.337500095367432</v>
+        <v>3.302005290985107</v>
       </c>
       <c r="G8" t="n">
-        <v>131.0899963378906</v>
+        <v>129.8463897705078</v>
       </c>
       <c r="H8" t="n">
-        <v>38700</v>
+        <v>32219.73828125</v>
       </c>
       <c r="I8" t="n">
         <v>22.18666648864746</v>
       </c>
       <c r="J8" t="n">
-        <v>46.93000030517578</v>
+        <v>40.38895797729492</v>
       </c>
       <c r="K8" t="n">
-        <v>289.4629211425781</v>
+        <v>275.384765625</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2506.85009765625</v>
       </c>
     </row>
     <row r="9">
@@ -727,34 +753,37 @@
         <v>43830</v>
       </c>
       <c r="B9" t="n">
-        <v>73.41249847412109</v>
+        <v>70.65937042236328</v>
       </c>
       <c r="C9" t="n">
-        <v>157.6999969482422</v>
+        <v>148.7892761230469</v>
       </c>
       <c r="D9" t="n">
-        <v>66.96949768066406</v>
+        <v>66.33824157714844</v>
       </c>
       <c r="E9" t="n">
         <v>92.39199829101562</v>
       </c>
       <c r="F9" t="n">
-        <v>5.882500171661377</v>
+        <v>5.842669010162354</v>
       </c>
       <c r="G9" t="n">
-        <v>205.25</v>
+        <v>203.3028106689453</v>
       </c>
       <c r="H9" t="n">
-        <v>55800</v>
+        <v>47835.0234375</v>
       </c>
       <c r="I9" t="n">
         <v>27.8886661529541</v>
       </c>
       <c r="J9" t="n">
-        <v>59.84999847412109</v>
+        <v>52.79319381713867</v>
       </c>
       <c r="K9" t="n">
-        <v>346.249267578125</v>
+        <v>330.3896484375</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3230.780029296875</v>
       </c>
     </row>
     <row r="10">
@@ -762,34 +791,37 @@
         <v>44196</v>
       </c>
       <c r="B10" t="n">
-        <v>132.6900024414062</v>
+        <v>128.8168029785156</v>
       </c>
       <c r="C10" t="n">
-        <v>222.4199981689453</v>
+        <v>212.0753936767578</v>
       </c>
       <c r="D10" t="n">
-        <v>87.63200378417969</v>
+        <v>86.80599212646484</v>
       </c>
       <c r="E10" t="n">
         <v>162.8464965820312</v>
       </c>
       <c r="F10" t="n">
-        <v>13.05500030517578</v>
+        <v>12.98799800872803</v>
       </c>
       <c r="G10" t="n">
-        <v>273.1600036621094</v>
+        <v>270.568603515625</v>
       </c>
       <c r="H10" t="n">
-        <v>81000</v>
+        <v>72634.5859375</v>
       </c>
       <c r="I10" t="n">
         <v>235.2233276367188</v>
       </c>
       <c r="J10" t="n">
-        <v>49.81999969482422</v>
+        <v>45.03853988647461</v>
       </c>
       <c r="K10" t="n">
-        <v>521.770751953125</v>
+        <v>499.3811645507812</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3756.070068359375</v>
       </c>
     </row>
     <row r="11">
@@ -797,34 +829,37 @@
         <v>44561</v>
       </c>
       <c r="B11" t="n">
-        <v>177.5700073242188</v>
+        <v>173.4494018554688</v>
       </c>
       <c r="C11" t="n">
-        <v>336.3200073242188</v>
+        <v>323.365966796875</v>
       </c>
       <c r="D11" t="n">
-        <v>144.8520050048828</v>
+        <v>143.4866333007812</v>
       </c>
       <c r="E11" t="n">
         <v>166.7169952392578</v>
       </c>
       <c r="F11" t="n">
-        <v>29.4109992980957</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="G11" t="n">
-        <v>336.3500061035156</v>
+        <v>333.1590881347656</v>
       </c>
       <c r="H11" t="n">
-        <v>78300</v>
+        <v>71495.8359375</v>
       </c>
       <c r="I11" t="n">
         <v>352.260009765625</v>
       </c>
       <c r="J11" t="n">
-        <v>51.5</v>
+        <v>47.76451110839844</v>
       </c>
       <c r="K11" t="n">
-        <v>421.1040344238281</v>
+        <v>404.2262878417969</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4766.18017578125</v>
       </c>
     </row>
     <row r="12">
@@ -832,34 +867,37 @@
         <v>44926</v>
       </c>
       <c r="B12" t="n">
-        <v>129.9299926757812</v>
+        <v>127.6515121459961</v>
       </c>
       <c r="C12" t="n">
-        <v>239.8200073242188</v>
+        <v>232.7434844970703</v>
       </c>
       <c r="D12" t="n">
-        <v>88.23000335693359</v>
+        <v>87.39834594726562</v>
       </c>
       <c r="E12" t="n">
         <v>84</v>
       </c>
       <c r="F12" t="n">
-        <v>14.61400032043457</v>
+        <v>14.56530284881592</v>
       </c>
       <c r="G12" t="n">
-        <v>120.3399963378906</v>
+        <v>119.1983489990234</v>
       </c>
       <c r="H12" t="n">
-        <v>55300</v>
+        <v>51738.21875</v>
       </c>
       <c r="I12" t="n">
         <v>123.1800003051758</v>
       </c>
       <c r="J12" t="n">
-        <v>26.43000030517578</v>
+        <v>25.48586082458496</v>
       </c>
       <c r="K12" t="n">
-        <v>317.2260437011719</v>
+        <v>306.0199584960938</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3839.5</v>
       </c>
     </row>
     <row r="13">
@@ -867,34 +905,37 @@
         <v>45291</v>
       </c>
       <c r="B13" t="n">
-        <v>192.5299987792969</v>
+        <v>190.2110137939453</v>
       </c>
       <c r="C13" t="n">
-        <v>376.0400085449219</v>
+        <v>368.1798706054688</v>
       </c>
       <c r="D13" t="n">
-        <v>139.6900024414062</v>
+        <v>138.373291015625</v>
       </c>
       <c r="E13" t="n">
         <v>151.9400024414062</v>
       </c>
       <c r="F13" t="n">
-        <v>49.52199935913086</v>
+        <v>49.37887191772461</v>
       </c>
       <c r="G13" t="n">
-        <v>353.9599914550781</v>
+        <v>350.6020202636719</v>
       </c>
       <c r="H13" t="n">
-        <v>78500</v>
+        <v>74979.453125</v>
       </c>
       <c r="I13" t="n">
         <v>248.4799957275391</v>
       </c>
       <c r="J13" t="n">
-        <v>50.25</v>
+        <v>49.58590316772461</v>
       </c>
       <c r="K13" t="n">
-        <v>293.6000061035156</v>
+        <v>285.2431945800781</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4769.830078125</v>
       </c>
     </row>
     <row r="14">
@@ -902,25 +943,25 @@
         <v>45657</v>
       </c>
       <c r="B14" t="n">
-        <v>250.4199981689453</v>
+        <v>248.6157989501953</v>
       </c>
       <c r="C14" t="n">
-        <v>421.5</v>
+        <v>415.7756652832031</v>
       </c>
       <c r="D14" t="n">
-        <v>189.3000030517578</v>
+        <v>188.1954040527344</v>
       </c>
       <c r="E14" t="n">
         <v>219.3899993896484</v>
       </c>
       <c r="F14" t="n">
-        <v>134.2899932861328</v>
+        <v>133.9398651123047</v>
       </c>
       <c r="G14" t="n">
-        <v>585.510009765625</v>
+        <v>582.1708374023438</v>
       </c>
       <c r="H14" t="n">
-        <v>53200</v>
+        <v>51911.93359375</v>
       </c>
       <c r="I14" t="n">
         <v>403.8399963378906</v>
@@ -929,7 +970,10 @@
         <v>20.04999923706055</v>
       </c>
       <c r="K14" t="n">
-        <v>419.7999877929688</v>
+        <v>411.3742065429688</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5881.6298828125</v>
       </c>
     </row>
     <row r="15">
@@ -937,25 +981,25 @@
         <v>46022</v>
       </c>
       <c r="B15" t="n">
-        <v>271.8599853515625</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="C15" t="n">
-        <v>483.6199951171875</v>
+        <v>480.5711669921875</v>
       </c>
       <c r="D15" t="n">
-        <v>313</v>
+        <v>312.3923034667969</v>
       </c>
       <c r="E15" t="n">
         <v>230.8200073242188</v>
       </c>
       <c r="F15" t="n">
-        <v>186.5</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="G15" t="n">
-        <v>660.0900268554688</v>
+        <v>658.3950805664062</v>
       </c>
       <c r="H15" t="n">
-        <v>119900</v>
+        <v>119520.53125</v>
       </c>
       <c r="I15" t="n">
         <v>449.7200012207031</v>
@@ -964,7 +1008,10 @@
         <v>36.90000152587891</v>
       </c>
       <c r="K15" t="n">
-        <v>599</v>
+        <v>592.1014404296875</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6845.5</v>
       </c>
     </row>
   </sheetData>

--- a/yearly.xlsx
+++ b/yearly.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Tencent</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -487,34 +487,34 @@
         <v>41274</v>
       </c>
       <c r="B2" t="n">
-        <v>16.05835914611816</v>
+        <v>16.0583610534668</v>
       </c>
       <c r="C2" t="n">
-        <v>21.37443923950195</v>
+        <v>21.37444114685059</v>
       </c>
       <c r="D2" t="n">
-        <v>17.53533935546875</v>
+        <v>17.53534507751465</v>
       </c>
       <c r="E2" t="n">
         <v>12.54349994659424</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2821623682975769</v>
+        <v>0.2821624577045441</v>
       </c>
       <c r="G2" t="n">
         <v>26.36746025085449</v>
       </c>
       <c r="H2" t="n">
-        <v>22761.587890625</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="I2" t="n">
         <v>2.257999897003174</v>
       </c>
       <c r="J2" t="n">
-        <v>14.74580478668213</v>
+        <v>14.74580383300781</v>
       </c>
       <c r="K2" t="n">
-        <v>42.95567321777344</v>
+        <v>2.290489673614502</v>
       </c>
       <c r="L2" t="n">
         <v>1426.18994140625</v>
@@ -525,34 +525,34 @@
         <v>41639</v>
       </c>
       <c r="B3" t="n">
-        <v>17.35419082641602</v>
+        <v>17.35419654846191</v>
       </c>
       <c r="C3" t="n">
-        <v>30.8428897857666</v>
+        <v>30.84288215637207</v>
       </c>
       <c r="D3" t="n">
-        <v>27.78143692016602</v>
+        <v>27.78143501281738</v>
       </c>
       <c r="E3" t="n">
         <v>19.93950080871582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3767540752887726</v>
+        <v>0.3767539858818054</v>
       </c>
       <c r="G3" t="n">
-        <v>54.13154602050781</v>
+        <v>54.13155364990234</v>
       </c>
       <c r="H3" t="n">
-        <v>20729.638671875</v>
+        <v>3.869999885559082</v>
       </c>
       <c r="I3" t="n">
         <v>10.02866744995117</v>
       </c>
       <c r="J3" t="n">
-        <v>19.30521774291992</v>
+        <v>19.30521583557129</v>
       </c>
       <c r="K3" t="n">
-        <v>85.64275360107422</v>
+        <v>3.910868883132935</v>
       </c>
       <c r="L3" t="n">
         <v>1848.359985351562</v>
@@ -569,28 +569,28 @@
         <v>39.3446044921875</v>
       </c>
       <c r="D4" t="n">
-        <v>26.28290367126465</v>
+        <v>26.28290176391602</v>
       </c>
       <c r="E4" t="n">
         <v>15.51749992370605</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4799688160419464</v>
+        <v>0.4799687266349792</v>
       </c>
       <c r="G4" t="n">
-        <v>77.27983093261719</v>
+        <v>77.27982330322266</v>
       </c>
       <c r="H4" t="n">
-        <v>20350.8203125</v>
+        <v>2.670000076293945</v>
       </c>
       <c r="I4" t="n">
         <v>14.82733345031738</v>
       </c>
       <c r="J4" t="n">
-        <v>27.84274673461914</v>
+        <v>27.84275054931641</v>
       </c>
       <c r="K4" t="n">
-        <v>97.63364410400391</v>
+        <v>7.556460380554199</v>
       </c>
       <c r="L4" t="n">
         <v>2058.89990234375</v>
@@ -601,34 +601,34 @@
         <v>42369</v>
       </c>
       <c r="B5" t="n">
-        <v>23.66843414306641</v>
+        <v>23.66843605041504</v>
       </c>
       <c r="C5" t="n">
         <v>48.27262496948242</v>
       </c>
       <c r="D5" t="n">
-        <v>38.5338249206543</v>
+        <v>38.53382873535156</v>
       </c>
       <c r="E5" t="n">
         <v>33.79449844360352</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8021025061607361</v>
+        <v>0.8021023869514465</v>
       </c>
       <c r="G5" t="n">
-        <v>103.6671142578125</v>
+        <v>103.667106628418</v>
       </c>
       <c r="H5" t="n">
-        <v>19648.85546875</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="I5" t="n">
         <v>16.00066757202148</v>
       </c>
       <c r="J5" t="n">
-        <v>27.2263240814209</v>
+        <v>27.22632598876953</v>
       </c>
       <c r="K5" t="n">
-        <v>132.6690673828125</v>
+        <v>11.03522872924805</v>
       </c>
       <c r="L5" t="n">
         <v>2043.93994140625</v>
@@ -639,34 +639,34 @@
         <v>42735</v>
       </c>
       <c r="B6" t="n">
-        <v>26.62235450744629</v>
+        <v>26.62235260009766</v>
       </c>
       <c r="C6" t="n">
-        <v>55.55104064941406</v>
+        <v>55.55105209350586</v>
       </c>
       <c r="D6" t="n">
-        <v>39.24901580810547</v>
+        <v>39.24901962280273</v>
       </c>
       <c r="E6" t="n">
         <v>37.49349975585938</v>
       </c>
       <c r="F6" t="n">
-        <v>2.622555732727051</v>
+        <v>2.62255597114563</v>
       </c>
       <c r="G6" t="n">
-        <v>113.9585342407227</v>
+        <v>113.9585571289062</v>
       </c>
       <c r="H6" t="n">
-        <v>28557.615234375</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="I6" t="n">
         <v>14.24600028991699</v>
       </c>
       <c r="J6" t="n">
-        <v>29.61037063598633</v>
+        <v>29.6103687286377</v>
       </c>
       <c r="K6" t="n">
-        <v>165.5685729980469</v>
+        <v>13.64457893371582</v>
       </c>
       <c r="L6" t="n">
         <v>2238.830078125</v>
@@ -677,34 +677,34 @@
         <v>43100</v>
       </c>
       <c r="B7" t="n">
-        <v>39.52470016479492</v>
+        <v>39.52470779418945</v>
       </c>
       <c r="C7" t="n">
-        <v>78.17729949951172</v>
+        <v>78.17732238769531</v>
       </c>
       <c r="D7" t="n">
-        <v>52.17353439331055</v>
+        <v>52.17352676391602</v>
       </c>
       <c r="E7" t="n">
         <v>58.4734992980957</v>
       </c>
       <c r="F7" t="n">
-        <v>4.772734642028809</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="G7" t="n">
-        <v>174.7859497070312</v>
+        <v>174.7859649658203</v>
       </c>
       <c r="H7" t="n">
-        <v>41112.21484375</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="I7" t="n">
         <v>20.75666618347168</v>
       </c>
       <c r="J7" t="n">
-        <v>38.75113296508789</v>
+        <v>38.75113677978516</v>
       </c>
       <c r="K7" t="n">
-        <v>355.2437438964844</v>
+        <v>20.21936225891113</v>
       </c>
       <c r="L7" t="n">
         <v>2673.610107421875</v>
@@ -715,25 +715,25 @@
         <v>43465</v>
       </c>
       <c r="B8" t="n">
-        <v>37.39425277709961</v>
+        <v>37.39424133300781</v>
       </c>
       <c r="C8" t="n">
         <v>94.43453979492188</v>
       </c>
       <c r="D8" t="n">
-        <v>51.75551223754883</v>
+        <v>51.75551605224609</v>
       </c>
       <c r="E8" t="n">
         <v>75.09850311279297</v>
       </c>
       <c r="F8" t="n">
-        <v>3.302005290985107</v>
+        <v>3.302005529403687</v>
       </c>
       <c r="G8" t="n">
         <v>129.8463897705078</v>
       </c>
       <c r="H8" t="n">
-        <v>32219.73828125</v>
+        <v>18.45999908447266</v>
       </c>
       <c r="I8" t="n">
         <v>22.18666648864746</v>
@@ -742,7 +742,7 @@
         <v>40.38895797729492</v>
       </c>
       <c r="K8" t="n">
-        <v>275.384765625</v>
+        <v>20.95170402526855</v>
       </c>
       <c r="L8" t="n">
         <v>2506.85009765625</v>
@@ -765,22 +765,22 @@
         <v>92.39199829101562</v>
       </c>
       <c r="F9" t="n">
-        <v>5.842669010162354</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="G9" t="n">
-        <v>203.3028106689453</v>
+        <v>203.3028259277344</v>
       </c>
       <c r="H9" t="n">
-        <v>47835.0234375</v>
+        <v>45.86000061035156</v>
       </c>
       <c r="I9" t="n">
         <v>27.8886661529541</v>
       </c>
       <c r="J9" t="n">
-        <v>52.79319381713867</v>
+        <v>52.79319763183594</v>
       </c>
       <c r="K9" t="n">
-        <v>330.3896484375</v>
+        <v>27.03851890563965</v>
       </c>
       <c r="L9" t="n">
         <v>3230.780029296875</v>
@@ -791,25 +791,25 @@
         <v>44196</v>
       </c>
       <c r="B10" t="n">
-        <v>128.8168029785156</v>
+        <v>128.8167572021484</v>
       </c>
       <c r="C10" t="n">
         <v>212.0753936767578</v>
       </c>
       <c r="D10" t="n">
-        <v>86.80599212646484</v>
+        <v>86.80597686767578</v>
       </c>
       <c r="E10" t="n">
         <v>162.8464965820312</v>
       </c>
       <c r="F10" t="n">
-        <v>12.98799800872803</v>
+        <v>12.98799705505371</v>
       </c>
       <c r="G10" t="n">
-        <v>270.568603515625</v>
+        <v>270.5685424804688</v>
       </c>
       <c r="H10" t="n">
-        <v>72634.5859375</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="I10" t="n">
         <v>235.2233276367188</v>
@@ -818,7 +818,7 @@
         <v>45.03853988647461</v>
       </c>
       <c r="K10" t="n">
-        <v>499.3811645507812</v>
+        <v>39.17340850830078</v>
       </c>
       <c r="L10" t="n">
         <v>3756.070068359375</v>
@@ -829,7 +829,7 @@
         <v>44561</v>
       </c>
       <c r="B11" t="n">
-        <v>173.4494018554688</v>
+        <v>173.4494476318359</v>
       </c>
       <c r="C11" t="n">
         <v>323.365966796875</v>
@@ -841,22 +841,22 @@
         <v>166.7169952392578</v>
       </c>
       <c r="F11" t="n">
-        <v>29.28561210632324</v>
+        <v>29.28560829162598</v>
       </c>
       <c r="G11" t="n">
         <v>333.1590881347656</v>
       </c>
       <c r="H11" t="n">
-        <v>71495.8359375</v>
+        <v>143.8999938964844</v>
       </c>
       <c r="I11" t="n">
         <v>352.260009765625</v>
       </c>
       <c r="J11" t="n">
-        <v>47.76451110839844</v>
+        <v>47.76452255249023</v>
       </c>
       <c r="K11" t="n">
-        <v>404.2262878417969</v>
+        <v>61.30045700073242</v>
       </c>
       <c r="L11" t="n">
         <v>4766.18017578125</v>
@@ -867,34 +867,34 @@
         <v>44926</v>
       </c>
       <c r="B12" t="n">
-        <v>127.6515121459961</v>
+        <v>127.6515045166016</v>
       </c>
       <c r="C12" t="n">
-        <v>232.7434844970703</v>
+        <v>232.7435150146484</v>
       </c>
       <c r="D12" t="n">
-        <v>87.39834594726562</v>
+        <v>87.39835357666016</v>
       </c>
       <c r="E12" t="n">
         <v>84</v>
       </c>
       <c r="F12" t="n">
-        <v>14.56530284881592</v>
+        <v>14.5653018951416</v>
       </c>
       <c r="G12" t="n">
         <v>119.1983489990234</v>
       </c>
       <c r="H12" t="n">
-        <v>51738.21875</v>
+        <v>64.76999664306641</v>
       </c>
       <c r="I12" t="n">
         <v>123.1800003051758</v>
       </c>
       <c r="J12" t="n">
-        <v>25.48586082458496</v>
+        <v>25.48586273193359</v>
       </c>
       <c r="K12" t="n">
-        <v>306.0199584960938</v>
+        <v>53.16610717773438</v>
       </c>
       <c r="L12" t="n">
         <v>3839.5</v>
@@ -905,25 +905,25 @@
         <v>45291</v>
       </c>
       <c r="B13" t="n">
-        <v>190.2110137939453</v>
+        <v>190.2110290527344</v>
       </c>
       <c r="C13" t="n">
-        <v>368.1798706054688</v>
+        <v>368.1799011230469</v>
       </c>
       <c r="D13" t="n">
-        <v>138.373291015625</v>
+        <v>138.3732757568359</v>
       </c>
       <c r="E13" t="n">
         <v>151.9400024414062</v>
       </c>
       <c r="F13" t="n">
-        <v>49.37887191772461</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="G13" t="n">
         <v>350.6020202636719</v>
       </c>
       <c r="H13" t="n">
-        <v>74979.453125</v>
+        <v>147.4100036621094</v>
       </c>
       <c r="I13" t="n">
         <v>248.4799957275391</v>
@@ -932,7 +932,7 @@
         <v>49.58590316772461</v>
       </c>
       <c r="K13" t="n">
-        <v>285.2431945800781</v>
+        <v>108.5568161010742</v>
       </c>
       <c r="L13" t="n">
         <v>4769.830078125</v>
@@ -946,7 +946,7 @@
         <v>248.6157989501953</v>
       </c>
       <c r="C14" t="n">
-        <v>415.7756652832031</v>
+        <v>415.7757263183594</v>
       </c>
       <c r="D14" t="n">
         <v>188.1954040527344</v>
@@ -958,10 +958,10 @@
         <v>133.9398651123047</v>
       </c>
       <c r="G14" t="n">
-        <v>582.1708374023438</v>
+        <v>582.1707763671875</v>
       </c>
       <c r="H14" t="n">
-        <v>51911.93359375</v>
+        <v>120.7900009155273</v>
       </c>
       <c r="I14" t="n">
         <v>403.8399963378906</v>
@@ -970,7 +970,7 @@
         <v>20.04999923706055</v>
       </c>
       <c r="K14" t="n">
-        <v>411.3742065429688</v>
+        <v>228.5044097900391</v>
       </c>
       <c r="L14" t="n">
         <v>5881.6298828125</v>
@@ -984,7 +984,7 @@
         <v>271.1220092773438</v>
       </c>
       <c r="C15" t="n">
-        <v>480.5711669921875</v>
+        <v>480.5711364746094</v>
       </c>
       <c r="D15" t="n">
         <v>312.3923034667969</v>
@@ -996,10 +996,10 @@
         <v>186.0646057128906</v>
       </c>
       <c r="G15" t="n">
-        <v>658.3950805664062</v>
+        <v>658.39501953125</v>
       </c>
       <c r="H15" t="n">
-        <v>119520.53125</v>
+        <v>214.1600036621094</v>
       </c>
       <c r="I15" t="n">
         <v>449.7200012207031</v>
@@ -1008,10 +1008,48 @@
         <v>36.90000152587891</v>
       </c>
       <c r="K15" t="n">
-        <v>592.1014404296875</v>
+        <v>344.2030029296875</v>
       </c>
       <c r="L15" t="n">
         <v>6845.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46387</v>
+      </c>
+      <c r="B16" t="n">
+        <v>342.9599914550781</v>
+      </c>
+      <c r="C16" t="n">
+        <v>533.6900024414062</v>
+      </c>
+      <c r="D16" t="n">
+        <v>347.6400146484375</v>
+      </c>
+      <c r="E16" t="n">
+        <v>254.0800018310547</v>
+      </c>
+      <c r="F16" t="n">
+        <v>221.3000030517578</v>
+      </c>
+      <c r="G16" t="n">
+        <v>737.5399780273438</v>
+      </c>
+      <c r="H16" t="n">
+        <v>570.8200073242188</v>
+      </c>
+      <c r="I16" t="n">
+        <v>367.1600036621094</v>
+      </c>
+      <c r="J16" t="n">
+        <v>98.12000274658203</v>
+      </c>
+      <c r="K16" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="L16" t="n">
+        <v>7718.93994140625</v>
       </c>
     </row>
   </sheetData>

--- a/yearly.xlsx
+++ b/yearly.xlsx
@@ -490,19 +490,19 @@
         <v>16.0583610534668</v>
       </c>
       <c r="C2" t="n">
-        <v>21.37444114685059</v>
+        <v>21.37443351745605</v>
       </c>
       <c r="D2" t="n">
-        <v>17.53534507751465</v>
+        <v>17.53534126281738</v>
       </c>
       <c r="E2" t="n">
         <v>12.54349994659424</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2821624577045441</v>
+        <v>0.2821624875068665</v>
       </c>
       <c r="G2" t="n">
-        <v>26.36746025085449</v>
+        <v>26.36746215820312</v>
       </c>
       <c r="H2" t="n">
         <v>2.400000095367432</v>
@@ -514,7 +514,7 @@
         <v>14.74580383300781</v>
       </c>
       <c r="K2" t="n">
-        <v>2.290489673614502</v>
+        <v>2.290488958358765</v>
       </c>
       <c r="L2" t="n">
         <v>1426.18994140625</v>
@@ -525,10 +525,10 @@
         <v>41639</v>
       </c>
       <c r="B3" t="n">
-        <v>17.35419654846191</v>
+        <v>17.35419082641602</v>
       </c>
       <c r="C3" t="n">
-        <v>30.84288215637207</v>
+        <v>30.84289169311523</v>
       </c>
       <c r="D3" t="n">
         <v>27.78143501281738</v>
@@ -537,10 +537,10 @@
         <v>19.93950080871582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3767539858818054</v>
+        <v>0.3767540156841278</v>
       </c>
       <c r="G3" t="n">
-        <v>54.13155364990234</v>
+        <v>54.13154983520508</v>
       </c>
       <c r="H3" t="n">
         <v>3.869999885559082</v>
@@ -549,10 +549,10 @@
         <v>10.02866744995117</v>
       </c>
       <c r="J3" t="n">
-        <v>19.30521583557129</v>
+        <v>19.30521392822266</v>
       </c>
       <c r="K3" t="n">
-        <v>3.910868883132935</v>
+        <v>3.910867214202881</v>
       </c>
       <c r="L3" t="n">
         <v>1848.359985351562</v>
@@ -563,7 +563,7 @@
         <v>42004</v>
       </c>
       <c r="B4" t="n">
-        <v>24.40390014648438</v>
+        <v>24.40389633178711</v>
       </c>
       <c r="C4" t="n">
         <v>39.3446044921875</v>
@@ -578,7 +578,7 @@
         <v>0.4799687266349792</v>
       </c>
       <c r="G4" t="n">
-        <v>77.27982330322266</v>
+        <v>77.27983856201172</v>
       </c>
       <c r="H4" t="n">
         <v>2.670000076293945</v>
@@ -587,7 +587,7 @@
         <v>14.82733345031738</v>
       </c>
       <c r="J4" t="n">
-        <v>27.84275054931641</v>
+        <v>27.84275245666504</v>
       </c>
       <c r="K4" t="n">
         <v>7.556460380554199</v>
@@ -601,22 +601,22 @@
         <v>42369</v>
       </c>
       <c r="B5" t="n">
-        <v>23.66843605041504</v>
+        <v>23.66843414306641</v>
       </c>
       <c r="C5" t="n">
-        <v>48.27262496948242</v>
+        <v>48.27261734008789</v>
       </c>
       <c r="D5" t="n">
-        <v>38.53382873535156</v>
+        <v>38.53383255004883</v>
       </c>
       <c r="E5" t="n">
         <v>33.79449844360352</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8021023869514465</v>
+        <v>0.8021025061607361</v>
       </c>
       <c r="G5" t="n">
-        <v>103.667106628418</v>
+        <v>103.667121887207</v>
       </c>
       <c r="H5" t="n">
         <v>2.869999885559082</v>
@@ -625,10 +625,10 @@
         <v>16.00066757202148</v>
       </c>
       <c r="J5" t="n">
-        <v>27.22632598876953</v>
+        <v>27.22631645202637</v>
       </c>
       <c r="K5" t="n">
-        <v>11.03522872924805</v>
+        <v>11.03522968292236</v>
       </c>
       <c r="L5" t="n">
         <v>2043.93994140625</v>
@@ -639,10 +639,10 @@
         <v>42735</v>
       </c>
       <c r="B6" t="n">
-        <v>26.62235260009766</v>
+        <v>26.62235641479492</v>
       </c>
       <c r="C6" t="n">
-        <v>55.55105209350586</v>
+        <v>55.55104827880859</v>
       </c>
       <c r="D6" t="n">
         <v>39.24901962280273</v>
@@ -651,10 +651,10 @@
         <v>37.49349975585938</v>
       </c>
       <c r="F6" t="n">
-        <v>2.62255597114563</v>
+        <v>2.622557163238525</v>
       </c>
       <c r="G6" t="n">
-        <v>113.9585571289062</v>
+        <v>113.9585494995117</v>
       </c>
       <c r="H6" t="n">
         <v>11.34000015258789</v>
@@ -663,10 +663,10 @@
         <v>14.24600028991699</v>
       </c>
       <c r="J6" t="n">
-        <v>29.6103687286377</v>
+        <v>29.6103630065918</v>
       </c>
       <c r="K6" t="n">
-        <v>13.64457893371582</v>
+        <v>13.64457702636719</v>
       </c>
       <c r="L6" t="n">
         <v>2238.830078125</v>
@@ -677,10 +677,10 @@
         <v>43100</v>
       </c>
       <c r="B7" t="n">
-        <v>39.52470779418945</v>
+        <v>39.52470397949219</v>
       </c>
       <c r="C7" t="n">
-        <v>78.17732238769531</v>
+        <v>78.17731475830078</v>
       </c>
       <c r="D7" t="n">
         <v>52.17352676391602</v>
@@ -689,7 +689,7 @@
         <v>58.4734992980957</v>
       </c>
       <c r="F7" t="n">
-        <v>4.772736072540283</v>
+        <v>4.772734642028809</v>
       </c>
       <c r="G7" t="n">
         <v>174.7859649658203</v>
@@ -701,10 +701,10 @@
         <v>20.75666618347168</v>
       </c>
       <c r="J7" t="n">
-        <v>38.75113677978516</v>
+        <v>38.75113296508789</v>
       </c>
       <c r="K7" t="n">
-        <v>20.21936225891113</v>
+        <v>20.21936416625977</v>
       </c>
       <c r="L7" t="n">
         <v>2673.610107421875</v>
@@ -715,22 +715,22 @@
         <v>43465</v>
       </c>
       <c r="B8" t="n">
-        <v>37.39424133300781</v>
+        <v>37.39424514770508</v>
       </c>
       <c r="C8" t="n">
-        <v>94.43453979492188</v>
+        <v>94.43452453613281</v>
       </c>
       <c r="D8" t="n">
-        <v>51.75551605224609</v>
+        <v>51.75551223754883</v>
       </c>
       <c r="E8" t="n">
         <v>75.09850311279297</v>
       </c>
       <c r="F8" t="n">
-        <v>3.302005529403687</v>
+        <v>3.302005290985107</v>
       </c>
       <c r="G8" t="n">
-        <v>129.8463897705078</v>
+        <v>129.8463592529297</v>
       </c>
       <c r="H8" t="n">
         <v>18.45999908447266</v>
@@ -739,10 +739,10 @@
         <v>22.18666648864746</v>
       </c>
       <c r="J8" t="n">
-        <v>40.38895797729492</v>
+        <v>40.38894271850586</v>
       </c>
       <c r="K8" t="n">
-        <v>20.95170402526855</v>
+        <v>20.95170021057129</v>
       </c>
       <c r="L8" t="n">
         <v>2506.85009765625</v>
@@ -753,19 +753,19 @@
         <v>43830</v>
       </c>
       <c r="B9" t="n">
-        <v>70.65937042236328</v>
+        <v>70.65935516357422</v>
       </c>
       <c r="C9" t="n">
-        <v>148.7892761230469</v>
+        <v>148.7892608642578</v>
       </c>
       <c r="D9" t="n">
-        <v>66.33824157714844</v>
+        <v>66.33824920654297</v>
       </c>
       <c r="E9" t="n">
         <v>92.39199829101562</v>
       </c>
       <c r="F9" t="n">
-        <v>5.842668533325195</v>
+        <v>5.842668056488037</v>
       </c>
       <c r="G9" t="n">
         <v>203.3028259277344</v>
@@ -777,10 +777,10 @@
         <v>27.8886661529541</v>
       </c>
       <c r="J9" t="n">
-        <v>52.79319763183594</v>
+        <v>52.79320526123047</v>
       </c>
       <c r="K9" t="n">
-        <v>27.03851890563965</v>
+        <v>27.03851699829102</v>
       </c>
       <c r="L9" t="n">
         <v>3230.780029296875</v>
@@ -791,22 +791,22 @@
         <v>44196</v>
       </c>
       <c r="B10" t="n">
-        <v>128.8167572021484</v>
+        <v>128.8167419433594</v>
       </c>
       <c r="C10" t="n">
-        <v>212.0753936767578</v>
+        <v>212.0753479003906</v>
       </c>
       <c r="D10" t="n">
-        <v>86.80597686767578</v>
+        <v>86.80598449707031</v>
       </c>
       <c r="E10" t="n">
         <v>162.8464965820312</v>
       </c>
       <c r="F10" t="n">
-        <v>12.98799705505371</v>
+        <v>12.98799896240234</v>
       </c>
       <c r="G10" t="n">
-        <v>270.5685424804688</v>
+        <v>270.5685729980469</v>
       </c>
       <c r="H10" t="n">
         <v>91.70999908447266</v>
@@ -815,7 +815,7 @@
         <v>235.2233276367188</v>
       </c>
       <c r="J10" t="n">
-        <v>45.03853988647461</v>
+        <v>45.03854370117188</v>
       </c>
       <c r="K10" t="n">
         <v>39.17340850830078</v>
@@ -829,13 +829,13 @@
         <v>44561</v>
       </c>
       <c r="B11" t="n">
-        <v>173.4494476318359</v>
+        <v>173.449462890625</v>
       </c>
       <c r="C11" t="n">
-        <v>323.365966796875</v>
+        <v>323.3659362792969</v>
       </c>
       <c r="D11" t="n">
-        <v>143.4866333007812</v>
+        <v>143.4866485595703</v>
       </c>
       <c r="E11" t="n">
         <v>166.7169952392578</v>
@@ -844,7 +844,7 @@
         <v>29.28560829162598</v>
       </c>
       <c r="G11" t="n">
-        <v>333.1590881347656</v>
+        <v>333.1590576171875</v>
       </c>
       <c r="H11" t="n">
         <v>143.8999938964844</v>
@@ -853,10 +853,10 @@
         <v>352.260009765625</v>
       </c>
       <c r="J11" t="n">
-        <v>47.76452255249023</v>
+        <v>47.76451873779297</v>
       </c>
       <c r="K11" t="n">
-        <v>61.30045700073242</v>
+        <v>61.30046844482422</v>
       </c>
       <c r="L11" t="n">
         <v>4766.18017578125</v>
@@ -870,7 +870,7 @@
         <v>127.6515045166016</v>
       </c>
       <c r="C12" t="n">
-        <v>232.7435150146484</v>
+        <v>232.7434844970703</v>
       </c>
       <c r="D12" t="n">
         <v>87.39835357666016</v>
@@ -879,7 +879,7 @@
         <v>84</v>
       </c>
       <c r="F12" t="n">
-        <v>14.5653018951416</v>
+        <v>14.56530094146729</v>
       </c>
       <c r="G12" t="n">
         <v>119.1983489990234</v>
@@ -891,10 +891,10 @@
         <v>123.1800003051758</v>
       </c>
       <c r="J12" t="n">
-        <v>25.48586273193359</v>
+        <v>25.48586082458496</v>
       </c>
       <c r="K12" t="n">
-        <v>53.16610717773438</v>
+        <v>53.16610336303711</v>
       </c>
       <c r="L12" t="n">
         <v>3839.5</v>
@@ -905,13 +905,13 @@
         <v>45291</v>
       </c>
       <c r="B13" t="n">
-        <v>190.2110290527344</v>
+        <v>190.2110443115234</v>
       </c>
       <c r="C13" t="n">
-        <v>368.1799011230469</v>
+        <v>368.1798706054688</v>
       </c>
       <c r="D13" t="n">
-        <v>138.3732757568359</v>
+        <v>138.373291015625</v>
       </c>
       <c r="E13" t="n">
         <v>151.9400024414062</v>
@@ -920,7 +920,7 @@
         <v>49.37887573242188</v>
       </c>
       <c r="G13" t="n">
-        <v>350.6020202636719</v>
+        <v>350.6019897460938</v>
       </c>
       <c r="H13" t="n">
         <v>147.4100036621094</v>
@@ -932,7 +932,7 @@
         <v>49.58590316772461</v>
       </c>
       <c r="K13" t="n">
-        <v>108.5568161010742</v>
+        <v>108.5568084716797</v>
       </c>
       <c r="L13" t="n">
         <v>4769.830078125</v>
@@ -949,16 +949,16 @@
         <v>415.7757263183594</v>
       </c>
       <c r="D14" t="n">
-        <v>188.1954040527344</v>
+        <v>188.1954345703125</v>
       </c>
       <c r="E14" t="n">
         <v>219.3899993896484</v>
       </c>
       <c r="F14" t="n">
-        <v>133.9398651123047</v>
+        <v>133.9398345947266</v>
       </c>
       <c r="G14" t="n">
-        <v>582.1707763671875</v>
+        <v>582.1708374023438</v>
       </c>
       <c r="H14" t="n">
         <v>120.7900009155273</v>
@@ -970,7 +970,7 @@
         <v>20.04999923706055</v>
       </c>
       <c r="K14" t="n">
-        <v>228.5044097900391</v>
+        <v>228.50439453125</v>
       </c>
       <c r="L14" t="n">
         <v>5881.6298828125</v>
@@ -996,7 +996,7 @@
         <v>186.0646057128906</v>
       </c>
       <c r="G15" t="n">
-        <v>658.39501953125</v>
+        <v>658.3950805664062</v>
       </c>
       <c r="H15" t="n">
         <v>214.1600036621094</v>
@@ -1019,37 +1019,37 @@
         <v>46387</v>
       </c>
       <c r="B16" t="n">
-        <v>342.9599914550781</v>
+        <v>333.0199890136719</v>
       </c>
       <c r="C16" t="n">
-        <v>533.6900024414062</v>
+        <v>512.9000244140625</v>
       </c>
       <c r="D16" t="n">
-        <v>347.6400146484375</v>
+        <v>344.0799865722656</v>
       </c>
       <c r="E16" t="n">
-        <v>254.0800018310547</v>
+        <v>249.1499938964844</v>
       </c>
       <c r="F16" t="n">
-        <v>221.3000030517578</v>
+        <v>228.3800048828125</v>
       </c>
       <c r="G16" t="n">
-        <v>737.5399780273438</v>
+        <v>725.1799926757812</v>
       </c>
       <c r="H16" t="n">
-        <v>570.8200073242188</v>
+        <v>611.760009765625</v>
       </c>
       <c r="I16" t="n">
-        <v>367.1600036621094</v>
+        <v>354.8099975585938</v>
       </c>
       <c r="J16" t="n">
-        <v>98.12000274658203</v>
+        <v>120.2300033569336</v>
       </c>
       <c r="K16" t="n">
-        <v>346.25</v>
+        <v>351.1900024414062</v>
       </c>
       <c r="L16" t="n">
-        <v>7718.93994140625</v>
+        <v>7651.5400390625</v>
       </c>
     </row>
   </sheetData>
